--- a/static/data/exports/Retro_PY_GE_2019.xlsx
+++ b/static/data/exports/Retro_PY_GE_2019.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -808,7 +808,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P18" t="n">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P20" t="n">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P21" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P22" t="n">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P26" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P28" t="n">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P29" t="n">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P30" t="n">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P31" t="n">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P33" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P34" t="n">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P69" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P70" t="n">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P71" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P72" t="n">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P73" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P74" t="n">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P75" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P76" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P77" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P78" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P80" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P84" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P85" t="n">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P86" t="n">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P89" t="n">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P90" t="n">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P91" t="n">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P92" t="n">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P93" t="n">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P94" t="n">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P95" t="n">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P99" t="n">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P102" t="n">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P103" t="n">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P110" t="n">
@@ -8680,7 +8680,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P111" t="n">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P112" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P116" t="n">
@@ -9130,7 +9130,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P119" t="n">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P121" t="n">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -9567,7 +9567,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P126" t="n">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P131" t="n">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P132" t="n">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P133" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P134" t="n">
@@ -10467,7 +10467,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P135" t="n">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P136" t="n">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P137" t="n">
@@ -10692,7 +10692,7 @@
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P138" t="n">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="O140" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P140" t="n">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -10979,7 +10979,7 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P142" t="n">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P143" t="n">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P144" t="n">
@@ -11204,7 +11204,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P145" t="n">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P146" t="n">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P147" t="n">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P148" t="n">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P149" t="n">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P150" t="n">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P151" t="n">
@@ -11729,7 +11729,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P152" t="n">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P153" t="n">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P154" t="n">
@@ -11954,7 +11954,7 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P155" t="n">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P156" t="n">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P157" t="n">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P159" t="n">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P161" t="n">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P162" t="n">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P163" t="n">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P165" t="n">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P166" t="n">
@@ -12841,7 +12841,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P167" t="n">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P168" t="n">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P169" t="n">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P170" t="n">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P171" t="n">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="O172" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P172" t="n">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P173" t="n">
@@ -13366,7 +13366,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P174" t="n">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P175" t="n">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P176" t="n">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P178" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P179" t="n">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P180" t="n">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P181" t="n">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P182" t="n">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P183" t="n">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P184" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P186" t="n">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P187" t="n">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P188" t="n">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P191" t="n">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P192" t="n">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P193" t="n">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P194" t="n">
@@ -14928,7 +14928,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -15065,7 +15065,7 @@
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -15215,7 +15215,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P199" t="n">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P200" t="n">
@@ -15365,7 +15365,7 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P201" t="n">
@@ -15440,7 +15440,7 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P202" t="n">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P203" t="n">
@@ -15590,7 +15590,7 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P204" t="n">
@@ -15665,7 +15665,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P205" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P207" t="n">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P208" t="n">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P209" t="n">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P210" t="n">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P211" t="n">
@@ -16190,7 +16190,7 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P212" t="n">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P213" t="n">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P214" t="n">
@@ -16477,7 +16477,7 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P216" t="n">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P217" t="n">
@@ -16627,7 +16627,7 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P218" t="n">
@@ -16702,7 +16702,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -16777,7 +16777,7 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P221" t="n">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -17002,7 +17002,7 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P224" t="n">
@@ -17152,7 +17152,7 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P225" t="n">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P226" t="n">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P227" t="n">
@@ -17377,7 +17377,7 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P228" t="n">
@@ -17452,7 +17452,7 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P229" t="n">
@@ -17527,7 +17527,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -17602,7 +17602,7 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P232" t="n">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -17889,7 +17889,7 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P235" t="n">
@@ -17964,7 +17964,7 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P236" t="n">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P237" t="n">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -18189,7 +18189,7 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P239" t="n">
@@ -18264,7 +18264,7 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -18414,7 +18414,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P242" t="n">
@@ -18489,7 +18489,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P243" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P244" t="n">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P245" t="n">
@@ -18714,7 +18714,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P246" t="n">
@@ -18789,7 +18789,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -18864,7 +18864,7 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P248" t="n">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P249" t="n">
@@ -19014,7 +19014,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P250" t="n">
@@ -19089,7 +19089,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P251" t="n">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P252" t="n">
@@ -19301,7 +19301,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P254" t="n">
@@ -19376,7 +19376,7 @@
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P256" t="n">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P257" t="n">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P258" t="n">
@@ -19676,7 +19676,7 @@
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P259" t="n">
@@ -19751,7 +19751,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P260" t="n">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P261" t="n">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P262" t="n">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P263" t="n">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P264" t="n">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P265" t="n">
@@ -20201,7 +20201,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P266" t="n">
@@ -20276,7 +20276,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P267" t="n">
@@ -20351,7 +20351,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P268" t="n">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P269" t="n">
@@ -20501,7 +20501,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P270" t="n">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P271" t="n">
@@ -20713,7 +20713,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P273" t="n">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P275" t="n">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P276" t="n">
@@ -21013,7 +21013,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P277" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P278" t="n">
@@ -21163,7 +21163,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P279" t="n">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -21313,7 +21313,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P281" t="n">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P282" t="n">
@@ -21463,7 +21463,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P283" t="n">
@@ -21538,7 +21538,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P284" t="n">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P285" t="n">
@@ -21688,7 +21688,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P286" t="n">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P287" t="n">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P288" t="n">
@@ -21913,7 +21913,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P289" t="n">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P290" t="n">
@@ -22125,7 +22125,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -22200,7 +22200,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -22275,7 +22275,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P294" t="n">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P295" t="n">
@@ -22425,7 +22425,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P296" t="n">
@@ -22500,7 +22500,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P298" t="n">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -22725,7 +22725,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P300" t="n">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P301" t="n">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P302" t="n">
@@ -22950,7 +22950,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P303" t="n">
@@ -23025,7 +23025,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P304" t="n">
@@ -23100,7 +23100,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P305" t="n">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P306" t="n">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P307" t="n">
@@ -23325,7 +23325,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P308" t="n">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P309" t="n">
@@ -23537,7 +23537,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P311" t="n">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P312" t="n">
@@ -23687,7 +23687,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P313" t="n">
@@ -23762,7 +23762,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P314" t="n">
@@ -23837,7 +23837,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P315" t="n">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P316" t="n">
@@ -23987,7 +23987,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P317" t="n">
@@ -24062,7 +24062,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -24137,7 +24137,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P320" t="n">
@@ -24287,7 +24287,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P321" t="n">
@@ -24362,7 +24362,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P322" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -24512,7 +24512,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P324" t="n">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P325" t="n">
@@ -24662,7 +24662,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P326" t="n">
@@ -24737,7 +24737,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P327" t="n">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P328" t="n">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P330" t="n">
@@ -25024,7 +25024,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P331" t="n">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P332" t="n">
@@ -25174,7 +25174,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P333" t="n">
@@ -25249,7 +25249,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P334" t="n">
@@ -25324,7 +25324,7 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -25399,7 +25399,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -25474,7 +25474,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P337" t="n">
@@ -25549,7 +25549,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P338" t="n">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P339" t="n">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P340" t="n">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P341" t="n">
@@ -25849,7 +25849,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P342" t="n">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P343" t="n">
@@ -25999,7 +25999,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P344" t="n">
@@ -26074,7 +26074,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P345" t="n">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P346" t="n">
@@ -26224,7 +26224,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P347" t="n">
@@ -26361,7 +26361,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P350" t="n">
@@ -26511,7 +26511,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P351" t="n">
@@ -26586,7 +26586,7 @@
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P352" t="n">
@@ -26661,7 +26661,7 @@
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P353" t="n">
@@ -26736,7 +26736,7 @@
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P354" t="n">
@@ -26811,7 +26811,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P355" t="n">
@@ -26886,7 +26886,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -26961,7 +26961,7 @@
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P357" t="n">
@@ -27036,7 +27036,7 @@
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P358" t="n">
@@ -27111,7 +27111,7 @@
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P359" t="n">
@@ -27186,7 +27186,7 @@
       </c>
       <c r="O360" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P360" t="n">
@@ -27261,7 +27261,7 @@
       </c>
       <c r="O361" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P361" t="n">
@@ -27336,7 +27336,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P362" t="n">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -27486,7 +27486,7 @@
       </c>
       <c r="O364" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P364" t="n">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="O365" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P365" t="n">
@@ -27636,7 +27636,7 @@
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -27773,7 +27773,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P368" t="n">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -27923,7 +27923,7 @@
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -27998,7 +27998,7 @@
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -28073,7 +28073,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P372" t="n">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="O373" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P373" t="n">
@@ -28223,7 +28223,7 @@
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -28298,7 +28298,7 @@
       </c>
       <c r="O375" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P375" t="n">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="O376" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P376" t="n">
@@ -28448,7 +28448,7 @@
       </c>
       <c r="O377" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P377" t="n">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="O378" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P378" t="n">
@@ -28598,7 +28598,7 @@
       </c>
       <c r="O379" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P379" t="n">
@@ -28673,7 +28673,7 @@
       </c>
       <c r="O380" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P380" t="n">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="O381" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P381" t="n">
@@ -28823,7 +28823,7 @@
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -28898,7 +28898,7 @@
       </c>
       <c r="O383" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P383" t="n">
@@ -28973,7 +28973,7 @@
       </c>
       <c r="O384" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P384" t="n">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="O385" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P385" t="n">
@@ -29185,7 +29185,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P387" t="n">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="O388" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P388" t="n">
@@ -29335,7 +29335,7 @@
       </c>
       <c r="O389" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P389" t="n">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="O390" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P390" t="n">
@@ -29485,7 +29485,7 @@
       </c>
       <c r="O391" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P391" t="n">
@@ -29560,7 +29560,7 @@
       </c>
       <c r="O392" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P392" t="n">
@@ -29635,7 +29635,7 @@
       </c>
       <c r="O393" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P393" t="n">
@@ -29710,7 +29710,7 @@
       </c>
       <c r="O394" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P394" t="n">
@@ -29785,7 +29785,7 @@
       </c>
       <c r="O395" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P395" t="n">
@@ -29860,7 +29860,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P396" t="n">
@@ -29935,7 +29935,7 @@
       </c>
       <c r="O397" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P397" t="n">
@@ -30010,7 +30010,7 @@
       </c>
       <c r="O398" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P398" t="n">
@@ -30085,7 +30085,7 @@
       </c>
       <c r="O399" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P399" t="n">
@@ -30160,7 +30160,7 @@
       </c>
       <c r="O400" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P400" t="n">
@@ -30235,7 +30235,7 @@
       </c>
       <c r="O401" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P401" t="n">
@@ -30310,7 +30310,7 @@
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -30385,7 +30385,7 @@
       </c>
       <c r="O403" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P403" t="n">
@@ -30460,7 +30460,7 @@
       </c>
       <c r="O404" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P404" t="n">
@@ -30597,7 +30597,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -30672,7 +30672,7 @@
       </c>
       <c r="O407" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P407" t="n">
@@ -30747,7 +30747,7 @@
       </c>
       <c r="O408" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P408" t="n">
@@ -30822,7 +30822,7 @@
       </c>
       <c r="O409" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P409" t="n">
@@ -30897,7 +30897,7 @@
       </c>
       <c r="O410" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P410" t="n">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P411" t="n">
@@ -31047,7 +31047,7 @@
       </c>
       <c r="O412" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P412" t="n">
@@ -31122,7 +31122,7 @@
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P413" t="n">
@@ -31197,7 +31197,7 @@
       </c>
       <c r="O414" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P414" t="n">
@@ -31272,7 +31272,7 @@
       </c>
       <c r="O415" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P415" t="n">
@@ -31347,7 +31347,7 @@
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -31422,7 +31422,7 @@
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -31497,7 +31497,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P418" t="n">
@@ -31572,7 +31572,7 @@
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P419" t="n">
@@ -31647,7 +31647,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="O421" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P421" t="n">
@@ -31797,7 +31797,7 @@
       </c>
       <c r="O422" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P422" t="n">
@@ -31872,7 +31872,7 @@
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -31947,7 +31947,7 @@
       </c>
       <c r="O424" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P424" t="n">
@@ -32084,7 +32084,7 @@
       </c>
       <c r="O426" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P426" t="n">
@@ -32159,7 +32159,7 @@
       </c>
       <c r="O427" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P427" t="n">
@@ -32234,7 +32234,7 @@
       </c>
       <c r="O428" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P428" t="n">
@@ -32309,7 +32309,7 @@
       </c>
       <c r="O429" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P429" t="n">
@@ -32384,7 +32384,7 @@
       </c>
       <c r="O430" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P430" t="n">
@@ -32459,7 +32459,7 @@
       </c>
       <c r="O431" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P431" t="n">
@@ -32534,7 +32534,7 @@
       </c>
       <c r="O432" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P432" t="n">
@@ -32609,7 +32609,7 @@
       </c>
       <c r="O433" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P433" t="n">
@@ -32684,7 +32684,7 @@
       </c>
       <c r="O434" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P434" t="n">
@@ -32759,7 +32759,7 @@
       </c>
       <c r="O435" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P435" t="n">
@@ -32834,7 +32834,7 @@
       </c>
       <c r="O436" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P436" t="n">
@@ -32909,7 +32909,7 @@
       </c>
       <c r="O437" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P437" t="n">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="O438" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P438" t="n">
@@ -33059,7 +33059,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P439" t="n">
@@ -33134,7 +33134,7 @@
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P440" t="n">
@@ -33209,7 +33209,7 @@
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -33284,7 +33284,7 @@
       </c>
       <c r="O442" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P442" t="n">
@@ -33421,7 +33421,7 @@
       </c>
       <c r="O444" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P444" t="n">
@@ -33496,7 +33496,7 @@
       </c>
       <c r="O445" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P445" t="n">
@@ -33571,7 +33571,7 @@
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P446" t="n">
@@ -33646,7 +33646,7 @@
       </c>
       <c r="O447" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P447" t="n">
@@ -33721,7 +33721,7 @@
       </c>
       <c r="O448" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P448" t="n">
@@ -33796,7 +33796,7 @@
       </c>
       <c r="O449" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P449" t="n">
@@ -33871,7 +33871,7 @@
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -33946,7 +33946,7 @@
       </c>
       <c r="O451" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P451" t="n">
@@ -34021,7 +34021,7 @@
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P452" t="n">
@@ -34096,7 +34096,7 @@
       </c>
       <c r="O453" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P453" t="n">
@@ -34171,7 +34171,7 @@
       </c>
       <c r="O454" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P454" t="n">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P455" t="n">
@@ -34321,7 +34321,7 @@
       </c>
       <c r="O456" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P456" t="n">
@@ -34396,7 +34396,7 @@
       </c>
       <c r="O457" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P457" t="n">
@@ -34471,7 +34471,7 @@
       </c>
       <c r="O458" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P458" t="n">
@@ -34546,7 +34546,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P459" t="n">
@@ -34621,7 +34621,7 @@
       </c>
       <c r="O460" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P460" t="n">
@@ -34696,7 +34696,7 @@
       </c>
       <c r="O461" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P461" t="n">
@@ -34771,7 +34771,7 @@
       </c>
       <c r="O462" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P462" t="n">
@@ -34908,7 +34908,7 @@
       </c>
       <c r="O464" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P464" t="n">
@@ -34983,7 +34983,7 @@
       </c>
       <c r="O465" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P465" t="n">
@@ -35058,7 +35058,7 @@
       </c>
       <c r="O466" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P466" t="n">
@@ -35133,7 +35133,7 @@
       </c>
       <c r="O467" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P467" t="n">
@@ -35208,7 +35208,7 @@
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -35283,7 +35283,7 @@
       </c>
       <c r="O469" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P469" t="n">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="O470" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P470" t="n">
@@ -35433,7 +35433,7 @@
       </c>
       <c r="O471" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P471" t="n">
@@ -35508,7 +35508,7 @@
       </c>
       <c r="O472" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P472" t="n">
@@ -35583,7 +35583,7 @@
       </c>
       <c r="O473" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P473" t="n">
@@ -35658,7 +35658,7 @@
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P474" t="n">
@@ -35733,7 +35733,7 @@
       </c>
       <c r="O475" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P475" t="n">
@@ -35808,7 +35808,7 @@
       </c>
       <c r="O476" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P476" t="n">
@@ -35883,7 +35883,7 @@
       </c>
       <c r="O477" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P477" t="n">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="O478" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P478" t="n">
@@ -36033,7 +36033,7 @@
       </c>
       <c r="O479" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P479" t="n">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="O480" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P480" t="n">
@@ -36245,7 +36245,7 @@
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P482" t="n">
@@ -36320,7 +36320,7 @@
       </c>
       <c r="O483" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P483" t="n">
@@ -36395,7 +36395,7 @@
       </c>
       <c r="O484" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P484" t="n">
@@ -36470,7 +36470,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -36545,7 +36545,7 @@
       </c>
       <c r="O486" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P486" t="n">
@@ -36620,7 +36620,7 @@
       </c>
       <c r="O487" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P487" t="n">
@@ -36695,7 +36695,7 @@
       </c>
       <c r="O488" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P488" t="n">
@@ -36770,7 +36770,7 @@
       </c>
       <c r="O489" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P489" t="n">
@@ -36845,7 +36845,7 @@
       </c>
       <c r="O490" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P490" t="n">
@@ -36920,7 +36920,7 @@
       </c>
       <c r="O491" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P491" t="n">
@@ -36995,7 +36995,7 @@
       </c>
       <c r="O492" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P492" t="n">
@@ -37070,7 +37070,7 @@
       </c>
       <c r="O493" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P493" t="n">
@@ -37145,7 +37145,7 @@
       </c>
       <c r="O494" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P494" t="n">
@@ -37220,7 +37220,7 @@
       </c>
       <c r="O495" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P495" t="n">
@@ -37295,7 +37295,7 @@
       </c>
       <c r="O496" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P496" t="n">
@@ -37370,7 +37370,7 @@
       </c>
       <c r="O497" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P497" t="n">
@@ -37445,7 +37445,7 @@
       </c>
       <c r="O498" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P498" t="n">
@@ -37520,7 +37520,7 @@
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P499" t="n">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P501" t="n">
@@ -37732,7 +37732,7 @@
       </c>
       <c r="O502" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P502" t="n">
@@ -37807,7 +37807,7 @@
       </c>
       <c r="O503" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P503" t="n">
@@ -37882,7 +37882,7 @@
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P504" t="n">
@@ -37957,7 +37957,7 @@
       </c>
       <c r="O505" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P505" t="n">
@@ -38032,7 +38032,7 @@
       </c>
       <c r="O506" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P506" t="n">
@@ -38107,7 +38107,7 @@
       </c>
       <c r="O507" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P507" t="n">
@@ -38182,7 +38182,7 @@
       </c>
       <c r="O508" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P508" t="n">
@@ -38257,7 +38257,7 @@
       </c>
       <c r="O509" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P509" t="n">
@@ -38332,7 +38332,7 @@
       </c>
       <c r="O510" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P510" t="n">
@@ -38407,7 +38407,7 @@
       </c>
       <c r="O511" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P511" t="n">
@@ -38482,7 +38482,7 @@
       </c>
       <c r="O512" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P512" t="n">
@@ -38557,7 +38557,7 @@
       </c>
       <c r="O513" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P513" t="n">
@@ -38632,7 +38632,7 @@
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P514" t="n">
@@ -38707,7 +38707,7 @@
       </c>
       <c r="O515" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P515" t="n">
@@ -38782,7 +38782,7 @@
       </c>
       <c r="O516" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P516" t="n">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P517" t="n">
@@ -38932,7 +38932,7 @@
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P518" t="n">
@@ -39007,7 +39007,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P519" t="n">
@@ -39144,7 +39144,7 @@
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P521" t="n">
@@ -39219,7 +39219,7 @@
       </c>
       <c r="O522" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P522" t="n">
@@ -39294,7 +39294,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P523" t="n">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="O524" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P524" t="n">
@@ -39444,7 +39444,7 @@
       </c>
       <c r="O525" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P525" t="n">
@@ -39519,7 +39519,7 @@
       </c>
       <c r="O526" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P526" t="n">
@@ -39594,7 +39594,7 @@
       </c>
       <c r="O527" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P527" t="n">
@@ -39669,7 +39669,7 @@
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P528" t="n">
@@ -39744,7 +39744,7 @@
       </c>
       <c r="O529" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P529" t="n">
@@ -39819,7 +39819,7 @@
       </c>
       <c r="O530" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P530" t="n">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="O531" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P531" t="n">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="O532" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P532" t="n">
@@ -40044,7 +40044,7 @@
       </c>
       <c r="O533" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P533" t="n">
@@ -40119,7 +40119,7 @@
       </c>
       <c r="O534" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P534" t="n">
@@ -40194,7 +40194,7 @@
       </c>
       <c r="O535" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P535" t="n">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="O536" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P536" t="n">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P538" t="n">
@@ -40481,7 +40481,7 @@
       </c>
       <c r="O539" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P539" t="n">
@@ -40556,7 +40556,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P540" t="n">
@@ -40631,7 +40631,7 @@
       </c>
       <c r="O541" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P541" t="n">
@@ -40706,7 +40706,7 @@
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P542" t="n">
@@ -40781,7 +40781,7 @@
       </c>
       <c r="O543" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P543" t="n">
@@ -40856,7 +40856,7 @@
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P544" t="n">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P545" t="n">
@@ -41006,7 +41006,7 @@
       </c>
       <c r="O546" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P546" t="n">
@@ -41081,7 +41081,7 @@
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P547" t="n">
@@ -41156,7 +41156,7 @@
       </c>
       <c r="O548" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P548" t="n">
@@ -41231,7 +41231,7 @@
       </c>
       <c r="O549" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P549" t="n">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="O550" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P550" t="n">
@@ -41381,7 +41381,7 @@
       </c>
       <c r="O551" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P551" t="n">
@@ -41456,7 +41456,7 @@
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P552" t="n">
@@ -41531,7 +41531,7 @@
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P553" t="n">
@@ -41606,7 +41606,7 @@
       </c>
       <c r="O554" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P554" t="n">
@@ -41681,7 +41681,7 @@
       </c>
       <c r="O555" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P555" t="n">
@@ -41818,7 +41818,7 @@
       </c>
       <c r="O557" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P557" t="n">
@@ -41893,7 +41893,7 @@
       </c>
       <c r="O558" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P558" t="n">
@@ -41968,7 +41968,7 @@
       </c>
       <c r="O559" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P559" t="n">
@@ -42043,7 +42043,7 @@
       </c>
       <c r="O560" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P560" t="n">
@@ -42118,7 +42118,7 @@
       </c>
       <c r="O561" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P561" t="n">
@@ -42193,7 +42193,7 @@
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P562" t="n">
@@ -42268,7 +42268,7 @@
       </c>
       <c r="O563" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P563" t="n">
@@ -42343,7 +42343,7 @@
       </c>
       <c r="O564" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P564" t="n">
@@ -42418,7 +42418,7 @@
       </c>
       <c r="O565" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P565" t="n">
@@ -42493,7 +42493,7 @@
       </c>
       <c r="O566" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P566" t="n">
@@ -42568,7 +42568,7 @@
       </c>
       <c r="O567" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P567" t="n">
@@ -42643,7 +42643,7 @@
       </c>
       <c r="O568" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P568" t="n">
@@ -42718,7 +42718,7 @@
       </c>
       <c r="O569" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P569" t="n">
@@ -42793,7 +42793,7 @@
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FEMALE</t>
         </is>
       </c>
       <c r="P570" t="n">
@@ -42868,7 +42868,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MALE</t>
         </is>
       </c>
       <c r="P571" t="n">
